--- a/Document/Budget.xlsx
+++ b/Document/Budget.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Git_remote\Hyd_pressure\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TCi7-14700F\Documents\GitHub\RMUTT_O2_LDG\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75B1274B-03EC-4C5F-9B69-2CD8022E22BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755F002B-7B11-4CD1-B538-7C14B8D30B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{A302AEDA-F35B-4A17-9144-484EDA0C52E9}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="28785" windowHeight="15600" xr2:uid="{A302AEDA-F35B-4A17-9144-484EDA0C52E9}"/>
   </bookViews>
   <sheets>
     <sheet name="O2_landing-gear" sheetId="1" r:id="rId1"/>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
-  <si>
-    <t>PLC FX3U</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
   <si>
     <t>PSU 24V</t>
   </si>
@@ -90,7 +87,25 @@
     <t>transmission</t>
   </si>
   <si>
-    <t>Design</t>
+    <t>HMI 10.2</t>
+  </si>
+  <si>
+    <t>Switch hub</t>
+  </si>
+  <si>
+    <t>Bus</t>
+  </si>
+  <si>
+    <t>PLC FX3U LAN</t>
+  </si>
+  <si>
+    <t>Regurator 5V10A</t>
+  </si>
+  <si>
+    <t>Plug</t>
+  </si>
+  <si>
+    <t>Design gear</t>
   </si>
 </sst>
 </file>
@@ -141,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -149,6 +164,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,44 +505,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03086C42-8665-43AA-A4DF-D9CD6FD1A582}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.8984375" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>12</v>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="1">
         <f>B2*C2</f>
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1">
         <v>500</v>
@@ -530,13 +551,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D10" si="0">B3*C3</f>
+        <f t="shared" ref="D3:D14" si="0">B3*C3</f>
         <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1">
         <v>100</v>
@@ -551,7 +572,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1">
         <v>100</v>
@@ -566,7 +587,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>200</v>
@@ -580,79 +601,139 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1">
-        <v>10000</v>
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5">
+        <v>7000</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="0"/>
-        <v>10000</v>
+        <f t="shared" ref="D7:D9" si="1">B7*C7</f>
+        <v>7000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1">
-        <v>200</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1200</v>
+      </c>
+      <c r="C8" s="5">
         <v>1</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <f t="shared" si="1"/>
+        <v>1200</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="0"/>
-        <v>2000</v>
+        <f t="shared" si="1"/>
+        <v>6000</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>200</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1">
-        <v>2000</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1">
-        <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1">
-        <f>SUM(D2:D10)</f>
-        <v>17200</v>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="1">
+        <f>SUM(D2:D13)</f>
+        <v>23400</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -661,44 +742,44 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34263896-127A-4A72-938D-53E2B773681E}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.5" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>12</v>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <f>B2*C2</f>
-        <v>2000</v>
+        <f t="shared" ref="D2:D19" si="0">B2*C2</f>
+        <v>3000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1">
         <v>500</v>
@@ -707,13 +788,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D14" si="0">B3*C3</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1">
         <v>100</v>
@@ -728,7 +809,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1">
         <v>100</v>
@@ -743,7 +824,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>200</v>
@@ -758,17 +839,17 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1">
-        <v>10000</v>
+        <v>200</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -776,14 +857,14 @@
         <v>13</v>
       </c>
       <c r="B8" s="1">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -791,14 +872,14 @@
         <v>14</v>
       </c>
       <c r="B9" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -806,90 +887,165 @@
         <v>15</v>
       </c>
       <c r="B10" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="1">
-        <v>1500</v>
+      <c r="B11" s="5">
+        <v>7000</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1500</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2000</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1200</v>
+      </c>
+      <c r="C12" s="5">
         <v>1</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>7000</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1">
+        <v>295</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1">
+        <v>50</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="1">
+        <v>7400</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="1">
-        <v>2000</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1">
-        <f t="shared" si="0"/>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1">
-        <v>1000</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1">
-        <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="1">
-        <f>SUM(D2:D14)</f>
-        <v>22700</v>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="1">
+        <f>SUM(D2:D19)</f>
+        <v>36645</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A20:C20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
